--- a/docpool/2026-10-12_docpool_daily_reports.xlsx
+++ b/docpool/2026-10-12_docpool_daily_reports.xlsx
@@ -13,9 +13,9 @@
     <sheet name="99_메타" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_요약'!$A$1:$Q$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_데이터'!$A$1:$AG$203</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_이력'!$A$1:$AG$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_요약'!$A$1:$Q$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_데이터'!$A$1:$AG$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_이력'!$A$1:$AG$230</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'99_메타'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,13 +443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
@@ -770,22 +770,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KRX:443060</t>
-        </is>
-      </c>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LS증권 / NH투자증권 / 유안타증권 / 하나증권</t>
+          <t>메리츠증권 / 유안타증권 / 키움증권 / 현대차증권</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,24 +789,34 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>하향★★</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>불명</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="n">
+        <v>580000</v>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4개 증권사 동시</t>
+          <t>4개 증권사 동시; 목표주가 -21%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/217937</t>
+          <t>https://t.me/DOC_POOL/217659</t>
         </is>
       </c>
     </row>
@@ -821,7 +827,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
@@ -829,22 +835,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KRX:017670</t>
+          <t>KRX:443060</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DB증권 / NH투자증권 / 다올투자증권 / 메리츠증권</t>
+          <t>LS증권 / NH투자증권 / 유안타증권 / 하나증권</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -853,25 +859,15 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>125000</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>125000</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>4개 증권사 동시</t>
@@ -879,7 +875,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/218023</t>
+          <t>https://t.me/DOC_POOL/217937</t>
         </is>
       </c>
     </row>
@@ -890,7 +886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -898,10 +894,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KRX:017670</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>통신</t>
@@ -909,7 +909,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DB증권 / NH투자증권 / 메리츠증권</t>
+          <t>DB증권 / NH투자증권 / 다올투자증권 / 메리츠증권</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -929,22 +929,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>75000</v>
+        <v>125000</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>75000</v>
+        <v>125000</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3개 증권사 동시</t>
+          <t>4개 증권사 동시</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/217954</t>
+          <t>https://t.me/DOC_POOL/218023</t>
         </is>
       </c>
     </row>
@@ -963,22 +963,18 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KRX:005930</t>
-        </is>
-      </c>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IBK투자증권 / NH투자증권 / 키움증권</t>
+          <t>DB증권 / NH투자증권 / 메리츠증권</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -998,10 +994,10 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>460000</v>
+        <v>75000</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>460000</v>
+        <v>75000</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
@@ -1013,7 +1009,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/217653</t>
+          <t>https://t.me/DOC_POOL/217954</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
@@ -1032,18 +1028,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KRX:005930</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>자동차</t>
+          <t>반도체</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>메리츠증권 / 유안타증권 / 키움증권</t>
+          <t>IBK투자증권 / NH투자증권 / 키움증권</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1062,11 +1062,15 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="n">
+        <v>460000</v>
+      </c>
       <c r="N9" s="2" t="n">
-        <v>580000</v>
-      </c>
-      <c r="O9" s="3" t="inlineStr"/>
+        <v>460000</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>3개 증권사 동시</t>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/217659</t>
+          <t>https://t.me/DOC_POOL/217653</t>
         </is>
       </c>
     </row>
@@ -1738,28 +1742,28 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>바이넥스</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KRX:071970</t>
+          <t>KOSDAQ:053030</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>기계/방산</t>
+          <t>바이오/제약</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>현대차증권</t>
+          <t>흥국증권</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>하향★</t>
+          <t>하향★★</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1773,22 +1777,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>80000</v>
+        <v>13000</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>70000</v>
+        <v>10000</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-12.5</v>
+        <v>-23.1</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>목표주가 -12%</t>
+          <t>목표주가 -23%</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/217941</t>
+          <t>https://t.me/DOC_POOL/218359</t>
         </is>
       </c>
     </row>
@@ -1801,22 +1805,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KRX:081660</t>
+          <t>KRX:071970</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>의류/섬유</t>
+          <t>기계/방산</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>현대차증권</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1836,22 +1840,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>65000</v>
+        <v>80000</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>56000</v>
+        <v>70000</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>-13.8</v>
+        <v>-12.5</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>목표주가 -14%</t>
+          <t>목표주가 -12%</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://t.me/DOC_POOL/217995</t>
+          <t>https://t.me/DOC_POOL/217941</t>
         </is>
       </c>
     </row>
@@ -1859,31 +1863,69 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="3" t="n"/>
+      <c r="D23" t="n">
+        <v>22</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>미스토홀딩스</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>KRX:081660</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>의류/섬유</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NH투자증권</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>하향★</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>56000</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>목표주가 -14%</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/217995</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>섹터</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>건수</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>톤</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>한 줄</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="3" t="n"/>
@@ -1891,18 +1933,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>111</v>
+          <t>섹터</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>긍정</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>톤</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>한 줄</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="3" t="n"/>
@@ -1910,22 +1958,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>전략/매크로</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>긍정</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>지정학적 리스크와 환율 변동성 속에서 차별화된 실적 흐름과 밸류에이션 공방이 지속됩니다.</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="3" t="n"/>
@@ -1933,22 +1977,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>전략/매크로</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>긍정</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>통신 업종은 본업의 실적 정상화와 함께 AI 데이터센터(AIDC) 인프라 확장 계획이 본격화되고 있습니다.</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="3" t="n"/>
@@ -1960,7 +2000,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1979,18 +2019,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>긍정</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>반도체 업종은 AI 메모리 수요와 가격 상승세가 지속되며 대형주 및 소부장 전반의 이익 상향이 기대됩니다.</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="3" t="n"/>
@@ -1998,22 +2034,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>기계/방산</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>긍정</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>전력기기 및 방산 업종은 데이터센터 수요와 수주 모멘텀을 바탕으로 긍정적 시각이 우세합니다.</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="3" t="n"/>
@@ -2021,15 +2053,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>인터넷/SW</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>긍정</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2040,22 +2072,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>자동차</t>
+          <t>기계/방산</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>부정</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>자동차 업종은 환율 하락과 중국산 전기차와의 가격 경쟁 심화로 단기 실적 둔화 우려가 제기됩니다.</t>
-        </is>
-      </c>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="3" t="n"/>
@@ -2063,22 +2091,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>채권</t>
+          <t>인터넷/SW</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>중립</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>채권시장은 국채선물 하락과 금리 상승 압력 확대로 약세 및 혼조세를 기록했습니다.</t>
-        </is>
-      </c>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="3" t="n"/>
@@ -2090,7 +2114,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2105,11 +2129,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>유통/소비</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2124,22 +2148,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>운송</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>긍정</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>조선 업종은 AM 사업 확장과 글로벌 유지보수 기업 인수를 통한 신성장 동력 확보가 주목받고 있습니다.</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="3" t="n"/>
@@ -2147,11 +2167,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>철강/금속</t>
+          <t>유통/소비</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2166,15 +2186,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>운송</t>
+          <t>음식료</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>긍정</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2185,15 +2205,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>음식료</t>
+          <t>채권</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>긍정</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2204,15 +2224,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>퀀트/파생</t>
+          <t>철강/금속</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>긍정</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2223,11 +2243,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT하드웨어</t>
+          <t>바이오/제약</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2242,15 +2262,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>건설/건자재</t>
+          <t>IT하드웨어</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>긍정</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2261,11 +2281,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>건설/건자재</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2280,15 +2300,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>바이오/제약</t>
+          <t>엔터/미디어/게임</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>긍정</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2299,15 +2319,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>엔터/미디어/게임</t>
+          <t>퀀트/파생</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>긍정</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2318,11 +2338,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>의류/섬유</t>
+          <t>화장품/생활용품</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2337,7 +2357,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>화장품/생활용품</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2356,7 +2376,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>화학/정유</t>
+          <t>로봇/AI</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2372,8 +2392,46 @@
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="3" t="n"/>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>의류/섬유</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>화학/정유</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q48"/>
+  <autoFilter ref="A1:Q50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2384,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG203"/>
+  <dimension ref="A1:AG230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27905,8 +27963,3675 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B204" t="n">
+        <v>218340</v>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>46307.5640162037</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>데일리_산업별_이슈_및_코멘트_유안타증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>유안타증권</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>유안타증권 리서치센터</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Yuanta Daily Sector News &amp; Data (2026년 10월 12일)</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr"/>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S204" s="3" t="inlineStr"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>1. LG에너지솔루션은 북미 ESS 시장 성장에 힘입어 3분기 매출 9조 6천억 원으로 역대 최대 실적을 달성함.</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>2. ASML은 유지보수용 노광장비 부품 가격을 10% 일괄 인상했으며, TSMC는 3분기 사상 최대 매출을 기록함.</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>3. AI 데이터센터 전력 수요 급증으로 미국 전력망 확충이 가속화되며 국내 전력기기 업체의 수혜가 지속됨.</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>AI 산업 확장에 따른 전력 인프라 수요와 반도체·이차전지 기업들의 실적 차별화가 섹터별 주가 흐름을 결정하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 3분기 매출 9조 6천억 원 | ASML 부품값 인상률 10% | 삼성전자 3분기 영업이익 107.4조 원 | 싱가폴 복합정제마진 10월 1주 9.3달러</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>삼성전자, TSMC, ASML, 현대차</t>
+        </is>
+      </c>
+      <c r="AD204" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218340</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218340_데일리_산업별_이슈_및_코멘트_유안타증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B205" t="n">
+        <v>218344</v>
+      </c>
+      <c r="C205" s="5" t="n">
+        <v>46307.56408564815</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>두산테스나_김동관_두산테스나_제품_포트폴리오_확장_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>IT하드웨어</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>KOSDAQ:131970</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>메리츠증권</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>김동관</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>제품 포트폴리오 확장 초입</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="n">
+        <v>169000</v>
+      </c>
+      <c r="Q205" s="2" t="inlineStr"/>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S205" s="3" t="inlineStr"/>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>3분기 매출액 770억원, 영업이익 33억원으로 컨센서스 하회 전망</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>4분기부터 ADAS 물량 회복 및 LPU 신규 양산으로 실적 개선 기대</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>2027년 LPU, CIS, 차세대 ADAS 등 제품 포트폴리오 확장으로 성장</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>단기 실적은 부진하나 신규 제품 양산과 고객사 다변화로 중장기 성장 방향성은 유효함.</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>3분기 매출액 770억원 | 3분기 영업이익 33억원 | 목표주가 169000원 | 2027년 영업이익 1301억원</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" s="6" t="n">
+        <v>746.9</v>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218344</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218344_두산테스나_김동관_두산테스나_제품_포트폴리오_확장_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B206" t="n">
+        <v>218351</v>
+      </c>
+      <c r="C206" s="5" t="n">
+        <v>46307.56456018519</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>마켓뷰_마켓_뷰_오픈AI발_거품론_미래에셋대우_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>전략/매크로</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>전략/매크로</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>미래에셋증권</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>김주연</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>오픈AI발 ‘거품론’</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S206" s="3" t="inlineStr"/>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>1. 코스피 지수는 반도체 TOP2 종목이 오픈AI발 거품론을 소화하며 2%대 하락함.</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>2. 10월 1~10일 수출액은 전년 동기 대비 102% 증가하며 역대 최대치를 기록함.</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>3. AI 데이터센터 확산에 따른 ESS 관련주와 중동 정세 불안으로 해운 테마가 강세임.</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>반도체 대형주 조정 속에서도 수출 호조와 AI 인프라 및 해운 테마 중심의 선별적 대응이 필요한 시점입니다.</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>10월 1~10일 수출 증가율 102% | 코스피 하락률 2.32% | 반도체 수출 증가율 170.9% | 한화M&amp;S 공개매수 금액 1,285억원</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 에이피알, 대화제약, HMM</t>
+        </is>
+      </c>
+      <c r="AD206" s="6" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218351</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218351_마켓뷰_마켓_뷰_오픈AI발_거품론_미래에셋대우_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B207" t="n">
+        <v>218355</v>
+      </c>
+      <c r="C207" s="5" t="n">
+        <v>46307.56465277778</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>모닝미팅자료_현대차증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>자동차</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>현대차증권</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>장문수</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>현대차(005380): 파업과 환율로 낮아진 이익을 반영한 주가</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q207" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S207" s="3" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>1. 2026년 3분기 영업이익은 2.35조원으로 컨센서스를 16.6% 하회할 전망임.</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>2. 노조 파업에 따른 생산 차질 9만대와 원재료비 상승이 실적 부진의 주요 원인임.</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>3. Physical AI 구체화 및 자율주행 전략 가시화가 향후 주가 할증 요소로 작용할 전망임.</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>파업과 환율 악재가 주가에 상당 부분 반영되었으며, 향후 신사업 전략 가시화에 따른 주가 탄력 회복이 기대됨.</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>3분기 영업이익 2.35조원 | 생산 차질 9만대 | 목표주가 500,000원 | 영업이익률 5.5%</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>기아, 한화오션, 삼성중공업, HD현대마린엔진</t>
+        </is>
+      </c>
+      <c r="AD207" s="6" t="n">
+        <v>3383.1</v>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218355</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218355_모닝미팅자료_현대차증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B208" t="n">
+        <v>218359</v>
+      </c>
+      <c r="C208" s="5" t="n">
+        <v>46307.56473379629</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>바이넥스_제약바이오_화장품_이지원_바이넥스_중장기_수주_모멘텀_여전_흥국증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>바이오/제약</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>바이넥스</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>KOSDAQ:053030</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>흥국증권</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>이지원</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>중장기 수주 모멘텀 여전히 유효</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q208" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S208" s="3" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>2026년 2분기 연결 매출액은 EMA 실사에 따른 공장 셧다운 여파로 전년 동기 대비 15% 감소함.</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>2027년 상반기 중 FDA 실사 완료 후 추가 수주와 매출 확대가 원활히 이루어질 것으로 전망됨.</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>10,000원으로 목표주가를 하향하나, 생물보안법 수혜 및 CDMO 수주 경쟁력은 여전히 유효함.</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>일시적인 공장 셧다운으로 단기 실적은 부진하나, 중장기 CDMO 수주 모멘텀은 견고하여 이익 회복이 기대됨.</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2026년 2분기 영업이익 -92억원 | 2027년 예상 매출액 210십억원 | 목표주가 10000원 | 현재주가 6390원</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" s="6" t="n">
+        <v>893.6</v>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218359</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218359_바이넥스_제약바이오_화장품_이지원_바이넥스_중장기_수주_모멘텀_여전_흥국증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B209" t="n">
+        <v>218363</v>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>46307.56481481482</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>배기연_조선_Weekly_Weekly_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>KRX:329180</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>KRX</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>메리츠증권</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>배기연</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Weekly (10.12~10.16) “2026년 3분기 실적 프리뷰 모아보기”</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S209" s="3" t="inlineStr"/>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>1. HD현대중공업 3분기 영업이익은 조업일수 감소와 환율 하락 영향으로 컨센서스를 9.8% 하회할 전망이다.</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>2. 상선부문 구조적 가격 상승세는 2028년까지 지속될 것으로 기대되며 LNG선 수익성 개선이 예상된다.</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>3. 2026년 HD현대중공업 연간 영업이익은 3조 7,682억원으로 전년 대비 84.9% 성장이 전망된다.</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>조업일수 감소와 환율 하락으로 인한 단기 실적 부진에도 불구하고 상선부문의 구조적 가격 상승세가 지속되어 중장기 성장성은 유효하다.</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>3분기 매출액 5조 5,892억원 | 3분기 영업이익 9,122억원 | 2026년 매출액 23조 5,719억원 | 2026년 영업이익 3조 7,682억원</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>삼성중공업, 한화오션, HD현대마린솔루션, STX엔진</t>
+        </is>
+      </c>
+      <c r="AD209" s="6" t="n">
+        <v>2574.7</v>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218363</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218363_배기연_조선_Weekly_Weekly_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B210" t="n">
+        <v>218367</v>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>46307.56488425926</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>산업_건설_건설부동산_Weekly_주가_조정을_매수_기회로_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>건설/건자재</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>류태환, 조유진</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>주가 조정을 매수 기회로</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S210" s="3" t="inlineStr"/>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>1. 건설업종 주가는 최근 조정받고 있으나 중장기 이익 회복 방향은 유효함.</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>2. 2027년 이후 실적 전망과 데이터센터 수주 여부가 기업 가치의 핵심 변수임.</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>3. 이익 전망이 유지되면서 밸류에이션 부담이 낮은 기업을 매수 기회로 활용해야 함.</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>단기 실적 변동성보다 중장기 이익 회복력과 밸류에이션 매력을 갖춘 기업 중심의 선별적 접근이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>서울 아파트 전용 84㎡ 평균 분양가 20억63만원 | 대우건설 P-CBO 발행 규모 335.5억원 | 대우건설 P-CBO 표면금리 5.09%</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A, 대우건설, GS건설, DL이앤씨</t>
+        </is>
+      </c>
+      <c r="AD210" s="6" t="n">
+        <v>1167.3</v>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218367</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218367_산업_건설_건설부동산_Weekly_주가_조정을_매수_기회로_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B211" t="n">
+        <v>218371</v>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>46307.56533564815</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>산업_기타_ESG_비싼_구주_값싼_신주_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>전략/매크로</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>오스템임플란트</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>엄수진</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>비싼 구주, 값싼 신주</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S211" s="3" t="inlineStr"/>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>1. 지배주주만 경영권 프리미엄을 독점하는 방식은 소액주주를 소외시키고 주주평등 원칙에 반함.</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2. 인수자가 지배주주 지분 매입 후 저가 유상증자로 신주를 취득해 일반주주 지분율 하락을 유발함.</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>3. 오스템임플란트 등 일부 기업은 소액주주에게도 동일한 프리미엄을 적용해 주주 가치를 제고함.</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>지배주주 중심의 M&amp;A 관행 개선과 소액주주 보호를 위한 의무공개매수제도 도입의 필요성이 커지고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>오스템임플란트 인수 가격 190000원 | 롯데렌탈 지배주주 인수 가격 77115원 | 미투온 제3자배정 신주 가격 2842원 | 베노티앤알 제3자배정 신주 가격 852원</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>롯데렌탈, 미투온, 베노티앤알, 토박스코리아</t>
+        </is>
+      </c>
+      <c r="AD211" s="6" t="n">
+        <v>719.6</v>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218371</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218371_산업_기타_ESG_비싼_구주_값싼_신주_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B212" t="n">
+        <v>218375</v>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>46307.56541666666</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>산업_기타_ESG_설탕값_10년_만의_급등_날씨_너머의_변수_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>음식료</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>CJ제일제당</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>박세연</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>설탕값 10년 만의 급등, 날씨 너머의 변수</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S212" s="3" t="inlineStr"/>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>달러</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>3분기 원당 선물 가격이 22.9% 급등하며 2016년 2분기 이후 최대 상승폭을 기록함.</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>9월 FAO 식량가격지수는 136.0으로 2022년 11월 이후 최고치를 경신함.</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>국제 설탕 가격 상승이 국내 식품 제조사 실적에 미치는 영향은 제한적일 것으로 판단함.</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>설탕값 급등보다 공급 정책, 환율, 국내 가격 조정이 식품사 원가에 미치는 영향이 중요함.</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>3분기 원당 상승률 22.9% | 9월 FAO 식량가격지수 136.0 | 9월 소비자물가 상승률 2.9% | 가공식품 물가 상승률 2.1%</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>삼양사, 오리온, 롯데웰푸드, 오뚜기</t>
+        </is>
+      </c>
+      <c r="AD212" s="6" t="n">
+        <v>656.5</v>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218375</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218375_산업_기타_ESG_설탕값_10년_만의_급등_날씨_너머의_변수_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B213" t="n">
+        <v>218379</v>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>46307.56549768519</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>산업_기타_디지털자산_디지털자산_Weekly_20261008_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>최윤영</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>디지털자산 Weekly (2026.10.08)</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr"/>
+      <c r="Q213" s="2" t="inlineStr"/>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S213" s="3" t="inlineStr"/>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>1. OKX와 ICE 합작사가 SEC 혁신면제를 활용해 63개 종목의 온체인 미국주식 거래 플랫폼 출시를 추진하며 제도권 편입이 본격화됨.</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>2. 솔라나 재단이 기관용 오픈소스 DvP 결제 프로그램을 공개해 기관의 도입 비용과 운영 부담을 완화할 수 있는 기반을 마련함.</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>3. 미국 FinCEN이 비수탁지갑 규제안을 철회하고 홍콩이 가상자산 인가제 도입을 추진하는 등 글로벌 규제 환경이 변화하고 있음.</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>토큰화 증권과 기관용 결제 인프라의 확산은 기존 금융과 온체인 거래의 결합을 가속화하며 제도권 금융 시장으로의 편입을 본격화하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>혁신면제 기간 5년 | 토큰화 대상 종목 63개 | 결제시간 단축 1~2일에서 수초 | 담보인정비율 20~100%</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>ICE, Solana Foundation, Binance, JPMorgan</t>
+        </is>
+      </c>
+      <c r="AD213" s="6" t="n">
+        <v>480.4</v>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218379</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218379_산업_기타_디지털자산_디지털자산_Weekly_20261008_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B214" t="n">
+        <v>218383</v>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>46307.5655787037</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>산업_기타_비로소_호시절_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>운송</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>박수영</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>항공 (Positive): 비로소 호시절</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr"/>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S214" s="3" t="inlineStr"/>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>1. 인바운드 수요 확대로 국제선 여객 수요의 구조적 성장 가속화</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2. 통합 대한항공 및 진에어 출범으로 국내 항공 시장 공급 경쟁 완화</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>3. 여객 수요 성장과 시장 재편 수혜로 대한항공과 제주항공 최선호</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>인바운드 수요의 구조적 성장과 항공 산업 내 공급자 축소로 국내 항공사들의 실적 개선이 본격화될 전망이다.</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>대한항공 목표주가 43000 | 진에어 목표주가 7500 | 제주항공 목표주가 6500 | 환율 1558</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>제주항공, 진에어</t>
+        </is>
+      </c>
+      <c r="AD214" s="6" t="n">
+        <v>4183</v>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218383</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218383_산업_기타_비로소_호시절_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B215" t="n">
+        <v>218387</v>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>46307.56563657407</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>산업_기타_스타링크_위성과_우주_주파수_모두_확보_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>스페이스X</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>정의훈</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>스타링크, 위성과 지상 주파수 모두 확보</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr"/>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S215" s="3" t="inlineStr"/>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>1만 5,000기 규모의 차세대 D2D 위성 배치를 미국 FCC가 부분 승인함</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2027년 이후 스타십 상용화와 연계해 광대역 데이터 및 IoT 서비스 제공 예정</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>위성과 지상 주파수를 모두 보유한 최초의 통신망 사업자로 시장 경쟁력 강화</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>스페이스X의 주파수 확보와 위성 배치는 기존 통신사에는 위협이나 D2D 밸류체인 전반에는 새로운 수요를 창출할 전망이다.</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>D2D 위성 승인 15000기 | 궤도 고도 330km | 프라임 대역 25MHz | 거래 종결 시점 2027년 11월</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" s="6" t="n">
+        <v>559.4</v>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218387</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218387_산업_기타_스타링크_위성과_우주_주파수_모두_확보_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B216" t="n">
+        <v>218391</v>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>46307.56609953703</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>산업_기타_안녕하세요_위클리에요로봇방산조선항공해운_2026100520261011_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>로봇/AI</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>양승윤, 임범수</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>안녕하십니까 로봇 위클리예요 (2026년 10월 2주차 주간 리포트)</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr"/>
+      <c r="Q216" s="2" t="inlineStr"/>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S216" s="3" t="inlineStr"/>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>1. 보스턴다이내믹스는 아마존 출신 Rohit Prasad를 신임 CEO로 선임하며 AI 기반의 로봇 양산 및 상용화 체제로 빠르게 전환 중이다.</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2. 한화에어로스페이스는 AUSA 전시회에서 K-9MH 실물을 전시하고 미 육군 자주포 사업 참여를 공식화하며 미국 시장 공략을 본격화한다.</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>3. 한국 조선업계는 군함 수출 시 단순 가격 경쟁력을 넘어 외교, 금융, 현지 생산 등 패키지 전략을 보강해야 유럽 시장 진입이 가능하다.</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>로봇과 방산 등 주요 산업에서 기술적 우위를 넘어 상용화와 현지화 전략이 기업의 핵심 경쟁력으로 부상하고 있다.</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>필드AI 기업가치 100억달러 | 한화에어로스페이스 K9MH 3대 추가 계약 | 바르질라 데이터센터향 엔진 수주 282MW | 팬오션 장기계약 1482억원</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>보스턴다이내믹스, HD현대중공업, 한화오션, 대한항공</t>
+        </is>
+      </c>
+      <c r="AD216" s="6" t="n">
+        <v>1259.4</v>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218391</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218391_산업_기타_안녕하세요_위클리에요로봇방산조선항공해운_2026100520261011_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B217" t="n">
+        <v>218395</v>
+      </c>
+      <c r="C217" s="5" t="n">
+        <v>46307.56616898148</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>산업_기타_우려는_충분히_반영됐다_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>유통/소비</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>파라다이스</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>임수진</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>레저, 우려는 충분히 반영됐다</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr"/>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S217" s="3" t="inlineStr"/>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>3분기 레저 업종은 인바운드 수요에도 홀드율과 고객 믹스에 따라 업체별 실적 차별화가 예상됨</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>4개사 목표주가는 업황을 반영해 하향 조정하며, 강원랜드와 GS피앤엘은 기존 목표주가를 유지함</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>레저 업종 주가는 매크로 및 규제 우려로 역사적 저점 수준이나, 우려는 충분히 반영된 것으로 판단됨</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>레저 업종은 매크로 우려로 주가가 역사적 저점이나, 인바운드 수요 회복과 조정안 발표 시 반등 가능성이 존재함.</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>파라다이스 3분기 영업이익 527억원 | 롯데관광개발 3분기 영업이익 366억원 | GKL 3분기 영업이익 149억원 | 강원랜드 3분기 영업이익 617억원</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>롯데관광개발, GKL, 하나투어, 강원랜드</t>
+        </is>
+      </c>
+      <c r="AD217" s="6" t="n">
+        <v>2537.3</v>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218395</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218395_산업_기타_우려는_충분히_반영됐다_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B218" t="n">
+        <v>218399</v>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>46307.56625</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>산업_기타_유럽_중국산_전기차_수출_장벽_확장_K배터리_수혜_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2차전지</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>한병화</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>유럽, 중국산 전기차 수출 장벽 확장, K 배터리 수혜</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr"/>
+      <c r="Q218" s="2" t="inlineStr"/>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S218" s="3" t="inlineStr"/>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>1. EU는 중국산 하이브리드 차량의 연간 수출대수를 4년간 50% 이상 축소하기로 합의하며 중국산 차량에 대한 수입 제한 조치를 강화함.</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2. 2026년 8월 기준 중국업체의 유럽 하이브리드 판매 점유율이 25.5%까지 급상승했으나, 향후 수출 제한으로 K배터리 수요 확대가 기대됨.</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>3. 2027년은 미국 전기차 시장 성장 전환과 유럽 내 점유율 회복이 맞물리며 K배터리 기업들이 제2의 전성기에 진입하는 원년이 될 전망임.</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>유럽의 중국산 전기차 규제 강화는 그간 중국산에 밀렸던 K배터리의 유럽 시장 점유율 회복과 실적 개선의 핵심 모멘텀이 될 것이다.</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>중국 하이브리드 점유율 25.5% | 유럽 전기차 판매 증가율 20% | 부품 조달 요건 70%</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>삼성SDI, SK온</t>
+        </is>
+      </c>
+      <c r="AD218" s="6" t="n">
+        <v>470.1</v>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218399</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218399_산업_기타_유럽_중국산_전기차_수출_장벽_확장_K배터리_수혜_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B219" t="n">
+        <v>218403</v>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>46307.56631944444</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>산업_미디어_희로애락_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>엔터/미디어/게임</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>CJ ENM</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>이현지, 고수영</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>CJ ENM / 스튜디오드래곤 3분기 프리뷰 및 업종 점검</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr"/>
+      <c r="Q219" s="2" t="inlineStr"/>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S219" s="3" t="inlineStr"/>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>1. TV 광고 업황은 부진이 지속되나 상반기 대비 역성장폭이 줄어들며 점진적인 반등이 기대됨.</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2. 스튜디오드래곤은 넷플릭스 오리지널 대작 방영 효과로 3분기 호실적이 예상됨.</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>3. CJ ENM은 내년부터 티빙과 피프스시즌의 본격적인 수익성 개선이 가시화될 전망임.</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>미디어 업종은 TV 광고 부진에도 불구하고 대작 콘텐츠 공급과 플랫폼 수익성 개선을 통해 바닥을 지나 점진적 회복세에 진입할 것으로 판단됨.</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>CJ ENM 3분기 매출액 1조 1,501억원 | CJ ENM 3분기 영업이익 189억원 | 스튜디오드래곤 3분기 매출액 1,850억원 | 스튜디오드래곤 3분기 영업이익 182억원</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>스튜디오드래곤</t>
+        </is>
+      </c>
+      <c r="AD219" s="6" t="n">
+        <v>935.2</v>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218403</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218403_산업_미디어_희로애락_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B220" t="n">
+        <v>218407</v>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>46307.56641203703</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>산업_반도체_IBKS_반도체_In_Depth_올_가을_단풍은_이천이_평택보다_더_곱다_IBK투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>김운호</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>올 가을 단풍은 이천이 평택보다 더 곱다</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr"/>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S220" s="3" t="inlineStr"/>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>1. AI 생태계 확대로 삼성전자와 SK하이닉스의 주주환원 규모가 사상 최대인 100조 원 수준으로 급증할 전망이다.</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2. SK하이닉스는 자사주 매입을, 삼성전자는 배당을 우선하는 주주환원 정책을 통해 밸류에이션 개선을 도모한다.</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>3. 시가총액 대비 주주환원 비율은 SK하이닉스 6.6%, 삼성전자 5.8%로 글로벌 빅테크 기업 대비 질적으로 우수하다.</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>AI 산업 성장에 따른 메모리 기업들의 사상 최대 주주환원 정책은 향후 밸류에이션 재평가의 핵심 동력이 될 것이다.</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>국내 메모리 주주환원 규모 100조 원 | SK하이닉스 시총 대비 주주환원율 6.6% | 삼성전자 시총 대비 주주환원율 5.8% | NVIDIA 자사주 매입 한도 1500억 달러</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>삼성전자, NVIDIA, Apple, Micron</t>
+        </is>
+      </c>
+      <c r="AD220" s="6" t="n">
+        <v>2394.4</v>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218407</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218407_산업_반도체_IBKS_반도체_In_Depth_올_가을_단풍은_이천이_평택보다_더_곱다_IBK투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B221" t="n">
+        <v>218411</v>
+      </c>
+      <c r="C221" s="5" t="n">
+        <v>46307.56688657407</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>산업_석유화학_기름뿜뿜_Weekly_미국_허리케인_상륙_대비_정제설비_타격_현실화_시_아비규환_불가피_iM증권_26.pdf</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>에너지/유틸</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>iM증권</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>전유진</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>러시아·중국 디젤 수출 중단 및 글로벌 정제설비 공급 차질 점검</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr"/>
+      <c r="Q221" s="2" t="inlineStr"/>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S221" s="3" t="inlineStr"/>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>1. 러시아와 중국의 디젤 수출 중단으로 동절기 디젤 가격 상방 압력 확대</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2. 미국 허리케인 영향으로 정제설비 타격 시 글로벌 정제품 재고 부족 심화</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>3. 정제품 가격 강세는 국내 정유사 마진 기회이나 인플레이션 압박도 동반</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>글로벌 정제설비 공급 차질과 주요국의 수출 제한이 겹치며 정제품 수급 불안과 인플레이션 압력이 가중되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>WTI 95.2달러 | 중국 7월 수출량 234만톤 | 중국 8월 수출량 460만톤 | 글로벌 공급차질 약 10%</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" s="6" t="n">
+        <v>4822.9</v>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218411</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218411_산업_석유화학_기름뿜뿜_Weekly_미국_허리케인_상륙_대비_정제설비_타격_현실화_시_아비규환_불가피_iM증권_26.pdf</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B222" t="n">
+        <v>218415</v>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>46307.56695601852</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>산업_에너지_Next_EnergyPower_Battery_Weekly_ESS_가스_발전의_경제성을_앞서기_시작.pdf</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2차전지</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>황성현</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>ESS, 가스 발전의 경제성을 앞서기 시작</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr"/>
+      <c r="Q222" s="2" t="inlineStr"/>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S222" s="3" t="inlineStr"/>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>1. 2026년 미국 신규 설비 기준 ESS 발전비용이 가스터빈 대비 65~75% 낮아 경제성 확보.</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2. AI 데이터센터 증설에 따른 전력수요 급증으로 가스터빈 공급 병목과 가격 상승 지속 전망.</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>3. 배터리 생산능력 확대와 기술 발전으로 ESS의 전력 인프라 내 수요 비중이 점진적 확대 예상.</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>가스터빈 공급 부족과 배터리 경제성 개선이 맞물리며 배터리 수요처가 전기차에서 전력 인프라로 본격 확장되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>ESS 발전비용 가스터빈 대비 65~75% 낮음 | 가스터빈 가격 2027년말 600달러/kW 예상 | 삼성SDI LFP 양극재 공급 계약 6조원</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>삼성SDI, LG화학, SK이노베이션, 두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="AD222" s="6" t="n">
+        <v>1063.3</v>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218415</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218415_산업_에너지_Next_EnergyPower_Battery_Weekly_ESS_가스_발전의_경제성을_앞서기_시작.pdf</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B223" t="n">
+        <v>218418</v>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>46307.56703703704</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>산업_에너지_Re_NEWable_Weekly_10월_3주차_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>에너지/유틸</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>교보증권</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>조혜빈</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Re-NEWable Weekly (10월 3주차 코멘트)</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr"/>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S223" s="3" t="inlineStr"/>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>2030년 국내 재생에너지 100GW 달성을 위해 2027년부터 연 10GW 이상, 2029~30년 연 15GW 확대를 목표로 설정함.</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>10년간 1,000조원을 투입하는 K-GX를 통해 태양광·풍력 핵심부품 국내생산세액공제 등 강력한 공급망 지원 정책을 추진함.</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>미국 태양광 제조 증설 계획의 70% 이상이 자금 미확보 또는 좌초 상태로, 실제 생산량과 발표 CAPA 간의 격차가 부각됨.</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>국내 재생에너지 확대 정책과 글로벌 공급망 규제 강화 속에서 핵심 부품 국산화 및 공급망 안정화가 산업 성장의 핵심 변수로 작용할 전망이다.</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2030년 재생에너지 목표 100GW | K-GX 투입 예산 1,000조원 | 미국 태양광 증설 계획 좌초 비중 70%</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>OCI홀딩스, SK이터닉스, HD현대에너지솔루션, 씨에스윈드</t>
+        </is>
+      </c>
+      <c r="AD223" s="6" t="n">
+        <v>4153.7</v>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218418</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218418_산업_에너지_Re_NEWable_Weekly_10월_3주차_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B224" t="n">
+        <v>218422</v>
+      </c>
+      <c r="C224" s="5" t="n">
+        <v>46307.56710648148</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>산업_음식료_키움_음식료_Weekly_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>음식료</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>박상준</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>키움 음식료 Weekly (10/12)</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr"/>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S224" s="3" t="inlineStr"/>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>1. 삼양식품은 신제품 짜장라면 '짜르르'를 내년 1분기 미국과 일본 시장에 출시해 프리미엄 라면 브랜드 확장을 추진할 계획입니다.</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2. KT&amp;G는 인도네시아 신공장 가동으로 연간 최대 350억 개비 생산 능력을 확보하며 해외 최대 생산 거점으로서의 입지를 강화했습니다.</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>3. CJ제일제당은 인도 벵갈루루에 '비비고 밥상' 1호점을 개장하며 K푸드 영토 확장을 가속화하고 현지 시장 공략을 본격화하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>국내 음식료 기업들이 해외 생산 거점 확대와 현지 맞춤형 신제품 출시를 통해 글로벌 시장 점유율을 적극적으로 높이고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>인도네시아 연간 최대 생산 능력 350억 개비 | 해외 설비 투자 총액 2조 4000억원 | 대인도 농식품 수출액 YoY 증가율 18.9% | 롯데웰푸드 빼빼로 광고 조회수 1000만뷰</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>KT&amp;G, CJ제일제당, 롯데웰푸드, 농심</t>
+        </is>
+      </c>
+      <c r="AD224" s="6" t="n">
+        <v>465.3</v>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218422</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218422_산업_음식료_키움_음식료_Weekly_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B225" t="n">
+        <v>218426</v>
+      </c>
+      <c r="C225" s="5" t="n">
+        <v>46307.56719907407</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>산업_자동차_수요는_못_바꿔도_물량은_되찾는다_하나증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>자동차</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>송선재</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>완성차 지역별 판매 동향 (2026년 9월): 수요는 못 바꿔도, 물량은 되찾는다</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr"/>
+      <c r="Q225" s="2" t="inlineStr"/>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S225" s="3" t="inlineStr"/>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>1. 현대차·기아 9월 합산 도매판매는 전년 대비 7% 감소하며 물량 기준 저성장이 지속됨.</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2. 산업수요 둔화와 경쟁 심화 외에도 생산 차질 및 모델 노후화가 실적에 복합적 영향을 미침.</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>3. 생산 차질 해소와 신차 출시 효과가 본격화되면서 향후 시장 점유율 반등이 기대됨.</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>생산 차질 해소와 신차 라인업 확대를 통해 완성차 업체의 시장 점유율 반등이 예상됩니다.</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>현대차 목표주가 510000 | 기아 목표주가 170000 | 현대차 9월 도매판매 308000대 | 기아 9월 도매판매 281000대</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="AD225" s="6" t="n">
+        <v>2770.1</v>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218426</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218426_산업_자동차_수요는_못_바꿔도_물량은_되찾는다_하나증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B226" t="n">
+        <v>218430</v>
+      </c>
+      <c r="C226" s="5" t="n">
+        <v>46307.56725694444</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>산업_제약_Kiwoom_Healthcare_종합정리_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>바이오/제약</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>허혜민, 신민수, 김종현</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Kiwoom Healthcare 종합정리 (2026년 10월 12일)</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr"/>
+      <c r="Q226" s="2" t="inlineStr"/>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S226" s="3" t="inlineStr"/>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>1. 한미약품 비만신약 에페가 국내 최초로 식약처 허가를 획득하며 상용화 사례를 기록함.</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2. 펩트론은 릴리와의 약물전달 플랫폼 기술평가를 종료했으나 협력 가능성은 열어둠.</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>3. 10월 초순 의료기기 수출 지표에서 필러와 덴탈 임플란트 등 주요 품목이 전년 대비 높은 성장세를 보임.</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>국내 제약·바이오 기업들의 신약 개발 성과와 의료기기 수출 지표의 견조한 흐름이 지속되고 있음.</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>에페 체중 감소율 9.75% | 알테오젠 투자 유치 2000억 원 | 10월 초순 필러 수출액 1억 1만 달러 | 10월 초순 덴탈 임플란트 수출액 2172만 달러</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>펩트론, 알테오젠, 오름테라퓨틱, 파마리서치</t>
+        </is>
+      </c>
+      <c r="AD226" s="6" t="n">
+        <v>1295.5</v>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218430</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218430_산업_제약_Kiwoom_Healthcare_종합정리_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B227" t="n">
+        <v>218434</v>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>46307.56770833334</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>산업_조선_한수위_FSRU_개조신조_수요_확대_SK증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>한승한</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>FSRU 개조&amp;신조 수요 확대</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr"/>
+      <c r="Q227" s="2" t="inlineStr"/>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S227" s="3" t="inlineStr"/>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>1. 글로벌 FSRU 수요가 신규 수입국 확대와 아시아 데이터센터 가스 수요 증가로 사상 최대치를 기록 중임.</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2. LNGC 신조 슬롯 부족과 빠른 인도 일정, 저렴한 비용으로 인해 단기적으로 개조 수요가 폭발적으로 증가하고 있음.</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>3. 한국 조선소는 LNGC 교체 물량 수주와 고사양 신조 FSRU 수주, 개조 사업 수혜로 장기적 성장이 기대됨.</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>FSRU 시장은 공급 부족으로 개조 수요가 단기적으로 시장을 주도하며, 향후 고사양 신조 발주로 이어지는 구조적 성장이 전망됨.</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>신조선가지수 186.73pt | 중고선가지수 224.04pt | FSRU 신조 계약선가 319.7~328.4백만달러 | 글로벌 FSRU 수주잔고 20척 근접 전망</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>한화엔진, HD현대마린솔루션</t>
+        </is>
+      </c>
+      <c r="AD227" s="6" t="n">
+        <v>797.8</v>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218434</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218434_산업_조선_한수위_FSRU_개조신조_수요_확대_SK증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B228" t="n">
+        <v>218438</v>
+      </c>
+      <c r="C228" s="5" t="n">
+        <v>46307.56778935185</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>산업_철강금속_Steel_Weekly_10월_2주차_iM증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>철강/금속</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>풍산</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>iM증권</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>김윤상</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>iM Steel Weekly (10월 2주): 미국 제외 글로벌 철강 업황 둔화 및 매크로 불확실성 지속</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr"/>
+      <c r="Q228" s="2" t="inlineStr"/>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S228" s="3" t="inlineStr"/>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>달러</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>1. 미국을 제외한 글로벌 철강 업황은 수요 부진과 원료탄 가격 약세로 전반적인 약보합세가 지속됨.</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2. 중국은 국경절 연휴 이후에도 거래가 한산하고 유통 재고가 크게 증가하며 업황 개선이 불투명함.</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>3. 국내 철강 유통 가격은 저가 수입재 유입 우려와 수요 부진으로 당분간 약세 흐름이 불가피함.</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>글로벌 철강 업황의 둔화와 매크로 불확실성이 지속되는 가운데, 국내 철강 업계는 수입재 유입과 수요 부진으로 당분간 정체 국면이 이어질 전망입니다.</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>베트남 열연가격 535달러 | 미국 8월 철강 수입량 235만숏톤 | 중국 철강재 유통재고 1251만톤 | 미시간대 기대인플레이션 1년 4.7%</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>부정</t>
+        </is>
+      </c>
+      <c r="AA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>현대제철, Arcelormittal, Nucor</t>
+        </is>
+      </c>
+      <c r="AD228" s="6" t="n">
+        <v>1938.7</v>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218438</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218438_산업_철강금속_Steel_Weekly_10월_2주차_iM증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B229" t="n">
+        <v>218442</v>
+      </c>
+      <c r="C229" s="5" t="n">
+        <v>46307.5678587963</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>산업_항공운송_Aviation_Industry_9월_항공_데이터_기록적인_3분기_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>운송</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>양승윤</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>9월 항공 데이터: 기록적인 3분기</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr"/>
+      <c r="Q229" s="2" t="inlineStr"/>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S229" s="3" t="inlineStr"/>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>3분기 국제선 여객은 2,636만명으로 분기 사상 최고치를 경신하며 견조한 수요를 기록함.</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>인천공항 화물 물동량은 27만톤으로 전년 대비 10% 증가하며 견조한 수준을 지속함.</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>대한항공은 AI·반도체 화물 수요와 아시아나항공 합병 시너지로 수익성 개선이 기대됨.</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>항공업종은 견조한 여객 수요와 화물 운임 강세에 힘입어 실적 호조가 지속될 전망입니다.</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>9월 국제선 여객 834만명 | 인천공항 화물 물동량 27만톤 | 3분기 국제선 여객 2636만명 | 10월 국제선 유류할증료 23단계</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>아시아나항공</t>
+        </is>
+      </c>
+      <c r="AD229" s="6" t="n">
+        <v>805.2</v>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218442</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218442_산업_항공운송_Aviation_Industry_9월_항공_데이터_기록적인_3분기_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B230" t="n">
+        <v>218446</v>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>46307.56792824074</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>산업_화장품_아마존_프라임데이_결과_코멘트_K_뷰티_good_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>화장품/생활용품</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>메디큐브</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>교보증권</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>권우정</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>아마존 프라임 빅딜데이 코멘트: 이번에도 대박</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr"/>
+      <c r="Q230" s="2" t="inlineStr"/>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S230" s="3" t="inlineStr"/>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>10월 아마존 프라임 빅딜데이 미국 Top 100 내 K-뷰티 비중은 B&amp;P 32%, 스킨케어 46%로 지난 6월 대비 각각 확대됨.</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>메디큐브는 6개국 아마존 B&amp;P Top 100 진입 SKU 수가 3월 38개에서 9월 93개로 폭발적 성장을 기록하며 시장 지배력 강화.</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>유럽 주요국 내 K-뷰티 브랜드들의 순위가 전반적으로 상승하며 북미를 넘어 유럽 시장으로의 확장세가 가속화되고 있음.</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>아마존 행사에서 확인된 K-뷰티의 글로벌 점유율 확대는 화장품 업종의 견조한 성장성을 증명하며 조정 시 매수 전략이 유효함을 시사함.</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>미국 스킨케어 K-뷰티 비중 46% | 메디큐브 6개국 진입 SKU 93개 | 미국 B&amp;P K-뷰티 비중 32% | 스페인 B&amp;P K-뷰티 비중 38%</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>아누아, 라네즈, 달바, 조선미녀</t>
+        </is>
+      </c>
+      <c r="AD230" s="6" t="n">
+        <v>555.2</v>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218446</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218446_산업_화장품_아마존_프라임데이_결과_코멘트_K_뷰티_good_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG203"/>
+  <autoFilter ref="A1:AG230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27917,7 +31642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG203"/>
+  <dimension ref="A1:AG230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -53438,8 +57163,3675 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B204" t="n">
+        <v>218340</v>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>46307.5640162037</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>데일리_산업별_이슈_및_코멘트_유안타증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>유안타증권</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>유안타증권 리서치센터</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Yuanta Daily Sector News &amp; Data (2026년 10월 12일)</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr"/>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S204" s="3" t="inlineStr"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>1. LG에너지솔루션은 북미 ESS 시장 성장에 힘입어 3분기 매출 9조 6천억 원으로 역대 최대 실적을 달성함.</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>2. ASML은 유지보수용 노광장비 부품 가격을 10% 일괄 인상했으며, TSMC는 3분기 사상 최대 매출을 기록함.</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>3. AI 데이터센터 전력 수요 급증으로 미국 전력망 확충이 가속화되며 국내 전력기기 업체의 수혜가 지속됨.</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>AI 산업 확장에 따른 전력 인프라 수요와 반도체·이차전지 기업들의 실적 차별화가 섹터별 주가 흐름을 결정하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션 3분기 매출 9조 6천억 원 | ASML 부품값 인상률 10% | 삼성전자 3분기 영업이익 107.4조 원 | 싱가폴 복합정제마진 10월 1주 9.3달러</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>삼성전자, TSMC, ASML, 현대차</t>
+        </is>
+      </c>
+      <c r="AD204" s="6" t="n">
+        <v>366</v>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218340</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218340_데일리_산업별_이슈_및_코멘트_유안타증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B205" t="n">
+        <v>218344</v>
+      </c>
+      <c r="C205" s="5" t="n">
+        <v>46307.56408564815</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>두산테스나_김동관_두산테스나_제품_포트폴리오_확장_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>IT하드웨어</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>KOSDAQ:131970</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>메리츠증권</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>김동관</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>제품 포트폴리오 확장 초입</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="n">
+        <v>169000</v>
+      </c>
+      <c r="Q205" s="2" t="inlineStr"/>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S205" s="3" t="inlineStr"/>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>3분기 매출액 770억원, 영업이익 33억원으로 컨센서스 하회 전망</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>4분기부터 ADAS 물량 회복 및 LPU 신규 양산으로 실적 개선 기대</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>2027년 LPU, CIS, 차세대 ADAS 등 제품 포트폴리오 확장으로 성장</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>단기 실적은 부진하나 신규 제품 양산과 고객사 다변화로 중장기 성장 방향성은 유효함.</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>3분기 매출액 770억원 | 3분기 영업이익 33억원 | 목표주가 169000원 | 2027년 영업이익 1301억원</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" s="6" t="n">
+        <v>746.9</v>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218344</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218344_두산테스나_김동관_두산테스나_제품_포트폴리오_확장_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B206" t="n">
+        <v>218351</v>
+      </c>
+      <c r="C206" s="5" t="n">
+        <v>46307.56456018519</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>마켓뷰_마켓_뷰_오픈AI발_거품론_미래에셋대우_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>전략/매크로</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>전략/매크로</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>미래에셋증권</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>김주연</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>오픈AI발 ‘거품론’</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S206" s="3" t="inlineStr"/>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>1. 코스피 지수는 반도체 TOP2 종목이 오픈AI발 거품론을 소화하며 2%대 하락함.</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>2. 10월 1~10일 수출액은 전년 동기 대비 102% 증가하며 역대 최대치를 기록함.</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>3. AI 데이터센터 확산에 따른 ESS 관련주와 중동 정세 불안으로 해운 테마가 강세임.</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>반도체 대형주 조정 속에서도 수출 호조와 AI 인프라 및 해운 테마 중심의 선별적 대응이 필요한 시점입니다.</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>10월 1~10일 수출 증가율 102% | 코스피 하락률 2.32% | 반도체 수출 증가율 170.9% | 한화M&amp;S 공개매수 금액 1,285억원</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 에이피알, 대화제약, HMM</t>
+        </is>
+      </c>
+      <c r="AD206" s="6" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218351</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218351_마켓뷰_마켓_뷰_오픈AI발_거품론_미래에셋대우_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B207" t="n">
+        <v>218355</v>
+      </c>
+      <c r="C207" s="5" t="n">
+        <v>46307.56465277778</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>모닝미팅자료_현대차증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>자동차</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>현대차증권</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>장문수</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>현대차(005380): 파업과 환율로 낮아진 이익을 반영한 주가</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q207" s="2" t="n">
+        <v>630000</v>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S207" s="3" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>1. 2026년 3분기 영업이익은 2.35조원으로 컨센서스를 16.6% 하회할 전망임.</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>2. 노조 파업에 따른 생산 차질 9만대와 원재료비 상승이 실적 부진의 주요 원인임.</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>3. Physical AI 구체화 및 자율주행 전략 가시화가 향후 주가 할증 요소로 작용할 전망임.</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>파업과 환율 악재가 주가에 상당 부분 반영되었으며, 향후 신사업 전략 가시화에 따른 주가 탄력 회복이 기대됨.</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>3분기 영업이익 2.35조원 | 생산 차질 9만대 | 목표주가 500,000원 | 영업이익률 5.5%</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>기아, 한화오션, 삼성중공업, HD현대마린엔진</t>
+        </is>
+      </c>
+      <c r="AD207" s="6" t="n">
+        <v>3383.1</v>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218355</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218355_모닝미팅자료_현대차증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B208" t="n">
+        <v>218359</v>
+      </c>
+      <c r="C208" s="5" t="n">
+        <v>46307.56473379629</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>바이넥스_제약바이오_화장품_이지원_바이넥스_중장기_수주_모멘텀_여전_흥국증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>바이오/제약</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>바이넥스</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>KOSDAQ:053030</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>흥국증권</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>이지원</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>중장기 수주 모멘텀 여전히 유효</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q208" s="2" t="n">
+        <v>13000</v>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S208" s="3" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>2026년 2분기 연결 매출액은 EMA 실사에 따른 공장 셧다운 여파로 전년 동기 대비 15% 감소함.</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>2027년 상반기 중 FDA 실사 완료 후 추가 수주와 매출 확대가 원활히 이루어질 것으로 전망됨.</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>10,000원으로 목표주가를 하향하나, 생물보안법 수혜 및 CDMO 수주 경쟁력은 여전히 유효함.</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>일시적인 공장 셧다운으로 단기 실적은 부진하나, 중장기 CDMO 수주 모멘텀은 견고하여 이익 회복이 기대됨.</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2026년 2분기 영업이익 -92억원 | 2027년 예상 매출액 210십억원 | 목표주가 10000원 | 현재주가 6390원</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" s="6" t="n">
+        <v>893.6</v>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218359</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218359_바이넥스_제약바이오_화장품_이지원_바이넥스_중장기_수주_모멘텀_여전_흥국증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B209" t="n">
+        <v>218363</v>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>46307.56481481482</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>배기연_조선_Weekly_Weekly_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>KRX:329180</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>KRX</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>메리츠증권</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>배기연</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Weekly (10.12~10.16) “2026년 3분기 실적 프리뷰 모아보기”</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S209" s="3" t="inlineStr"/>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>1. HD현대중공업 3분기 영업이익은 조업일수 감소와 환율 하락 영향으로 컨센서스를 9.8% 하회할 전망이다.</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>2. 상선부문 구조적 가격 상승세는 2028년까지 지속될 것으로 기대되며 LNG선 수익성 개선이 예상된다.</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>3. 2026년 HD현대중공업 연간 영업이익은 3조 7,682억원으로 전년 대비 84.9% 성장이 전망된다.</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>조업일수 감소와 환율 하락으로 인한 단기 실적 부진에도 불구하고 상선부문의 구조적 가격 상승세가 지속되어 중장기 성장성은 유효하다.</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>3분기 매출액 5조 5,892억원 | 3분기 영업이익 9,122억원 | 2026년 매출액 23조 5,719억원 | 2026년 영업이익 3조 7,682억원</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>삼성중공업, 한화오션, HD현대마린솔루션, STX엔진</t>
+        </is>
+      </c>
+      <c r="AD209" s="6" t="n">
+        <v>2574.7</v>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218363</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218363_배기연_조선_Weekly_Weekly_메리츠증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B210" t="n">
+        <v>218367</v>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>46307.56488425926</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>산업_건설_건설부동산_Weekly_주가_조정을_매수_기회로_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>건설/건자재</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>류태환, 조유진</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>주가 조정을 매수 기회로</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S210" s="3" t="inlineStr"/>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>1. 건설업종 주가는 최근 조정받고 있으나 중장기 이익 회복 방향은 유효함.</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>2. 2027년 이후 실적 전망과 데이터센터 수주 여부가 기업 가치의 핵심 변수임.</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>3. 이익 전망이 유지되면서 밸류에이션 부담이 낮은 기업을 매수 기회로 활용해야 함.</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>단기 실적 변동성보다 중장기 이익 회복력과 밸류에이션 매력을 갖춘 기업 중심의 선별적 접근이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>서울 아파트 전용 84㎡ 평균 분양가 20억63만원 | 대우건설 P-CBO 발행 규모 335.5억원 | 대우건설 P-CBO 표면금리 5.09%</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A, 대우건설, GS건설, DL이앤씨</t>
+        </is>
+      </c>
+      <c r="AD210" s="6" t="n">
+        <v>1167.3</v>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218367</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218367_산업_건설_건설부동산_Weekly_주가_조정을_매수_기회로_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B211" t="n">
+        <v>218371</v>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>46307.56533564815</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>산업_기타_ESG_비싼_구주_값싼_신주_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>전략/매크로</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>오스템임플란트</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>엄수진</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>비싼 구주, 값싼 신주</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S211" s="3" t="inlineStr"/>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>1. 지배주주만 경영권 프리미엄을 독점하는 방식은 소액주주를 소외시키고 주주평등 원칙에 반함.</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2. 인수자가 지배주주 지분 매입 후 저가 유상증자로 신주를 취득해 일반주주 지분율 하락을 유발함.</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>3. 오스템임플란트 등 일부 기업은 소액주주에게도 동일한 프리미엄을 적용해 주주 가치를 제고함.</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>지배주주 중심의 M&amp;A 관행 개선과 소액주주 보호를 위한 의무공개매수제도 도입의 필요성이 커지고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>오스템임플란트 인수 가격 190000원 | 롯데렌탈 지배주주 인수 가격 77115원 | 미투온 제3자배정 신주 가격 2842원 | 베노티앤알 제3자배정 신주 가격 852원</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>롯데렌탈, 미투온, 베노티앤알, 토박스코리아</t>
+        </is>
+      </c>
+      <c r="AD211" s="6" t="n">
+        <v>719.6</v>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218371</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218371_산업_기타_ESG_비싼_구주_값싼_신주_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B212" t="n">
+        <v>218375</v>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>46307.56541666666</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>산업_기타_ESG_설탕값_10년_만의_급등_날씨_너머의_변수_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>음식료</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>CJ제일제당</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>박세연</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>설탕값 10년 만의 급등, 날씨 너머의 변수</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S212" s="3" t="inlineStr"/>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>달러</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>3분기 원당 선물 가격이 22.9% 급등하며 2016년 2분기 이후 최대 상승폭을 기록함.</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>9월 FAO 식량가격지수는 136.0으로 2022년 11월 이후 최고치를 경신함.</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>국제 설탕 가격 상승이 국내 식품 제조사 실적에 미치는 영향은 제한적일 것으로 판단함.</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>설탕값 급등보다 공급 정책, 환율, 국내 가격 조정이 식품사 원가에 미치는 영향이 중요함.</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>3분기 원당 상승률 22.9% | 9월 FAO 식량가격지수 136.0 | 9월 소비자물가 상승률 2.9% | 가공식품 물가 상승률 2.1%</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>삼양사, 오리온, 롯데웰푸드, 오뚜기</t>
+        </is>
+      </c>
+      <c r="AD212" s="6" t="n">
+        <v>656.5</v>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218375</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218375_산업_기타_ESG_설탕값_10년_만의_급등_날씨_너머의_변수_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B213" t="n">
+        <v>218379</v>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>46307.56549768519</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>산업_기타_디지털자산_디지털자산_Weekly_20261008_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>최윤영</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>디지털자산 Weekly (2026.10.08)</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr"/>
+      <c r="Q213" s="2" t="inlineStr"/>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S213" s="3" t="inlineStr"/>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>1. OKX와 ICE 합작사가 SEC 혁신면제를 활용해 63개 종목의 온체인 미국주식 거래 플랫폼 출시를 추진하며 제도권 편입이 본격화됨.</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>2. 솔라나 재단이 기관용 오픈소스 DvP 결제 프로그램을 공개해 기관의 도입 비용과 운영 부담을 완화할 수 있는 기반을 마련함.</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>3. 미국 FinCEN이 비수탁지갑 규제안을 철회하고 홍콩이 가상자산 인가제 도입을 추진하는 등 글로벌 규제 환경이 변화하고 있음.</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>토큰화 증권과 기관용 결제 인프라의 확산은 기존 금융과 온체인 거래의 결합을 가속화하며 제도권 금융 시장으로의 편입을 본격화하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>혁신면제 기간 5년 | 토큰화 대상 종목 63개 | 결제시간 단축 1~2일에서 수초 | 담보인정비율 20~100%</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>ICE, Solana Foundation, Binance, JPMorgan</t>
+        </is>
+      </c>
+      <c r="AD213" s="6" t="n">
+        <v>480.4</v>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218379</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218379_산업_기타_디지털자산_디지털자산_Weekly_20261008_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B214" t="n">
+        <v>218383</v>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>46307.5655787037</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>산업_기타_비로소_호시절_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>운송</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>박수영</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>항공 (Positive): 비로소 호시절</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr"/>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S214" s="3" t="inlineStr"/>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>1. 인바운드 수요 확대로 국제선 여객 수요의 구조적 성장 가속화</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2. 통합 대한항공 및 진에어 출범으로 국내 항공 시장 공급 경쟁 완화</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>3. 여객 수요 성장과 시장 재편 수혜로 대한항공과 제주항공 최선호</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>인바운드 수요의 구조적 성장과 항공 산업 내 공급자 축소로 국내 항공사들의 실적 개선이 본격화될 전망이다.</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>대한항공 목표주가 43000 | 진에어 목표주가 7500 | 제주항공 목표주가 6500 | 환율 1558</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>제주항공, 진에어</t>
+        </is>
+      </c>
+      <c r="AD214" s="6" t="n">
+        <v>4183</v>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218383</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218383_산업_기타_비로소_호시절_한화투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B215" t="n">
+        <v>218387</v>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>46307.56563657407</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>산업_기타_스타링크_위성과_우주_주파수_모두_확보_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>스페이스X</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>정의훈</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>스타링크, 위성과 지상 주파수 모두 확보</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr"/>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S215" s="3" t="inlineStr"/>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>1만 5,000기 규모의 차세대 D2D 위성 배치를 미국 FCC가 부분 승인함</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2027년 이후 스타십 상용화와 연계해 광대역 데이터 및 IoT 서비스 제공 예정</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>위성과 지상 주파수를 모두 보유한 최초의 통신망 사업자로 시장 경쟁력 강화</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>스페이스X의 주파수 확보와 위성 배치는 기존 통신사에는 위협이나 D2D 밸류체인 전반에는 새로운 수요를 창출할 전망이다.</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>D2D 위성 승인 15000기 | 궤도 고도 330km | 프라임 대역 25MHz | 거래 종결 시점 2027년 11월</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" s="6" t="n">
+        <v>559.4</v>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218387</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218387_산업_기타_스타링크_위성과_우주_주파수_모두_확보_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B216" t="n">
+        <v>218391</v>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>46307.56609953703</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>산업_기타_안녕하세요_위클리에요로봇방산조선항공해운_2026100520261011_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>로봇/AI</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>양승윤, 임범수</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>안녕하십니까 로봇 위클리예요 (2026년 10월 2주차 주간 리포트)</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr"/>
+      <c r="Q216" s="2" t="inlineStr"/>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S216" s="3" t="inlineStr"/>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>1. 보스턴다이내믹스는 아마존 출신 Rohit Prasad를 신임 CEO로 선임하며 AI 기반의 로봇 양산 및 상용화 체제로 빠르게 전환 중이다.</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2. 한화에어로스페이스는 AUSA 전시회에서 K-9MH 실물을 전시하고 미 육군 자주포 사업 참여를 공식화하며 미국 시장 공략을 본격화한다.</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>3. 한국 조선업계는 군함 수출 시 단순 가격 경쟁력을 넘어 외교, 금융, 현지 생산 등 패키지 전략을 보강해야 유럽 시장 진입이 가능하다.</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>로봇과 방산 등 주요 산업에서 기술적 우위를 넘어 상용화와 현지화 전략이 기업의 핵심 경쟁력으로 부상하고 있다.</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>필드AI 기업가치 100억달러 | 한화에어로스페이스 K9MH 3대 추가 계약 | 바르질라 데이터센터향 엔진 수주 282MW | 팬오션 장기계약 1482억원</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>보스턴다이내믹스, HD현대중공업, 한화오션, 대한항공</t>
+        </is>
+      </c>
+      <c r="AD216" s="6" t="n">
+        <v>1259.4</v>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218391</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218391_산업_기타_안녕하세요_위클리에요로봇방산조선항공해운_2026100520261011_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B217" t="n">
+        <v>218395</v>
+      </c>
+      <c r="C217" s="5" t="n">
+        <v>46307.56616898148</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>산업_기타_우려는_충분히_반영됐다_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>유통/소비</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>파라다이스</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>임수진</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>레저, 우려는 충분히 반영됐다</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr"/>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S217" s="3" t="inlineStr"/>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>3분기 레저 업종은 인바운드 수요에도 홀드율과 고객 믹스에 따라 업체별 실적 차별화가 예상됨</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>4개사 목표주가는 업황을 반영해 하향 조정하며, 강원랜드와 GS피앤엘은 기존 목표주가를 유지함</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>레저 업종 주가는 매크로 및 규제 우려로 역사적 저점 수준이나, 우려는 충분히 반영된 것으로 판단됨</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>레저 업종은 매크로 우려로 주가가 역사적 저점이나, 인바운드 수요 회복과 조정안 발표 시 반등 가능성이 존재함.</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>파라다이스 3분기 영업이익 527억원 | 롯데관광개발 3분기 영업이익 366억원 | GKL 3분기 영업이익 149억원 | 강원랜드 3분기 영업이익 617억원</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>롯데관광개발, GKL, 하나투어, 강원랜드</t>
+        </is>
+      </c>
+      <c r="AD217" s="6" t="n">
+        <v>2537.3</v>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218395</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218395_산업_기타_우려는_충분히_반영됐다_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B218" t="n">
+        <v>218399</v>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>46307.56625</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>산업_기타_유럽_중국산_전기차_수출_장벽_확장_K배터리_수혜_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2차전지</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>한병화</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>유럽, 중국산 전기차 수출 장벽 확장, K 배터리 수혜</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr"/>
+      <c r="Q218" s="2" t="inlineStr"/>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S218" s="3" t="inlineStr"/>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>1. EU는 중국산 하이브리드 차량의 연간 수출대수를 4년간 50% 이상 축소하기로 합의하며 중국산 차량에 대한 수입 제한 조치를 강화함.</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2. 2026년 8월 기준 중국업체의 유럽 하이브리드 판매 점유율이 25.5%까지 급상승했으나, 향후 수출 제한으로 K배터리 수요 확대가 기대됨.</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>3. 2027년은 미국 전기차 시장 성장 전환과 유럽 내 점유율 회복이 맞물리며 K배터리 기업들이 제2의 전성기에 진입하는 원년이 될 전망임.</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>유럽의 중국산 전기차 규제 강화는 그간 중국산에 밀렸던 K배터리의 유럽 시장 점유율 회복과 실적 개선의 핵심 모멘텀이 될 것이다.</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>중국 하이브리드 점유율 25.5% | 유럽 전기차 판매 증가율 20% | 부품 조달 요건 70%</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>삼성SDI, SK온</t>
+        </is>
+      </c>
+      <c r="AD218" s="6" t="n">
+        <v>470.1</v>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218399</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218399_산업_기타_유럽_중국산_전기차_수출_장벽_확장_K배터리_수혜_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B219" t="n">
+        <v>218403</v>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>46307.56631944444</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>산업_미디어_희로애락_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>엔터/미디어/게임</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>CJ ENM</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>이현지, 고수영</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>CJ ENM / 스튜디오드래곤 3분기 프리뷰 및 업종 점검</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr"/>
+      <c r="Q219" s="2" t="inlineStr"/>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S219" s="3" t="inlineStr"/>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>1. TV 광고 업황은 부진이 지속되나 상반기 대비 역성장폭이 줄어들며 점진적인 반등이 기대됨.</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2. 스튜디오드래곤은 넷플릭스 오리지널 대작 방영 효과로 3분기 호실적이 예상됨.</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>3. CJ ENM은 내년부터 티빙과 피프스시즌의 본격적인 수익성 개선이 가시화될 전망임.</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>미디어 업종은 TV 광고 부진에도 불구하고 대작 콘텐츠 공급과 플랫폼 수익성 개선을 통해 바닥을 지나 점진적 회복세에 진입할 것으로 판단됨.</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>CJ ENM 3분기 매출액 1조 1,501억원 | CJ ENM 3분기 영업이익 189억원 | 스튜디오드래곤 3분기 매출액 1,850억원 | 스튜디오드래곤 3분기 영업이익 182억원</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>스튜디오드래곤</t>
+        </is>
+      </c>
+      <c r="AD219" s="6" t="n">
+        <v>935.2</v>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218403</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218403_산업_미디어_희로애락_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B220" t="n">
+        <v>218407</v>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>46307.56641203703</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>산업_반도체_IBKS_반도체_In_Depth_올_가을_단풍은_이천이_평택보다_더_곱다_IBK투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>김운호</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>올 가을 단풍은 이천이 평택보다 더 곱다</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr"/>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S220" s="3" t="inlineStr"/>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>1. AI 생태계 확대로 삼성전자와 SK하이닉스의 주주환원 규모가 사상 최대인 100조 원 수준으로 급증할 전망이다.</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2. SK하이닉스는 자사주 매입을, 삼성전자는 배당을 우선하는 주주환원 정책을 통해 밸류에이션 개선을 도모한다.</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>3. 시가총액 대비 주주환원 비율은 SK하이닉스 6.6%, 삼성전자 5.8%로 글로벌 빅테크 기업 대비 질적으로 우수하다.</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>AI 산업 성장에 따른 메모리 기업들의 사상 최대 주주환원 정책은 향후 밸류에이션 재평가의 핵심 동력이 될 것이다.</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>국내 메모리 주주환원 규모 100조 원 | SK하이닉스 시총 대비 주주환원율 6.6% | 삼성전자 시총 대비 주주환원율 5.8% | NVIDIA 자사주 매입 한도 1500억 달러</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>삼성전자, NVIDIA, Apple, Micron</t>
+        </is>
+      </c>
+      <c r="AD220" s="6" t="n">
+        <v>2394.4</v>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218407</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218407_산업_반도체_IBKS_반도체_In_Depth_올_가을_단풍은_이천이_평택보다_더_곱다_IBK투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B221" t="n">
+        <v>218411</v>
+      </c>
+      <c r="C221" s="5" t="n">
+        <v>46307.56688657407</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>산업_석유화학_기름뿜뿜_Weekly_미국_허리케인_상륙_대비_정제설비_타격_현실화_시_아비규환_불가피_iM증권_26.pdf</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>에너지/유틸</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>iM증권</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>전유진</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>러시아·중국 디젤 수출 중단 및 글로벌 정제설비 공급 차질 점검</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr"/>
+      <c r="Q221" s="2" t="inlineStr"/>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S221" s="3" t="inlineStr"/>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>1. 러시아와 중국의 디젤 수출 중단으로 동절기 디젤 가격 상방 압력 확대</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2. 미국 허리케인 영향으로 정제설비 타격 시 글로벌 정제품 재고 부족 심화</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>3. 정제품 가격 강세는 국내 정유사 마진 기회이나 인플레이션 압박도 동반</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>글로벌 정제설비 공급 차질과 주요국의 수출 제한이 겹치며 정제품 수급 불안과 인플레이션 압력이 가중되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>WTI 95.2달러 | 중국 7월 수출량 234만톤 | 중국 8월 수출량 460만톤 | 글로벌 공급차질 약 10%</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>중립</t>
+        </is>
+      </c>
+      <c r="AA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" s="6" t="n">
+        <v>4822.9</v>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218411</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218411_산업_석유화학_기름뿜뿜_Weekly_미국_허리케인_상륙_대비_정제설비_타격_현실화_시_아비규환_불가피_iM증권_26.pdf</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B222" t="n">
+        <v>218415</v>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>46307.56695601852</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>산업_에너지_Next_EnergyPower_Battery_Weekly_ESS_가스_발전의_경제성을_앞서기_시작.pdf</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2차전지</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>황성현</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>ESS, 가스 발전의 경제성을 앞서기 시작</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr"/>
+      <c r="Q222" s="2" t="inlineStr"/>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S222" s="3" t="inlineStr"/>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>1. 2026년 미국 신규 설비 기준 ESS 발전비용이 가스터빈 대비 65~75% 낮아 경제성 확보.</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2. AI 데이터센터 증설에 따른 전력수요 급증으로 가스터빈 공급 병목과 가격 상승 지속 전망.</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>3. 배터리 생산능력 확대와 기술 발전으로 ESS의 전력 인프라 내 수요 비중이 점진적 확대 예상.</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>가스터빈 공급 부족과 배터리 경제성 개선이 맞물리며 배터리 수요처가 전기차에서 전력 인프라로 본격 확장되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>ESS 발전비용 가스터빈 대비 65~75% 낮음 | 가스터빈 가격 2027년말 600달러/kW 예상 | 삼성SDI LFP 양극재 공급 계약 6조원</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>삼성SDI, LG화학, SK이노베이션, 두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="AD222" s="6" t="n">
+        <v>1063.3</v>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218415</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218415_산업_에너지_Next_EnergyPower_Battery_Weekly_ESS_가스_발전의_경제성을_앞서기_시작.pdf</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B223" t="n">
+        <v>218418</v>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>46307.56703703704</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>산업_에너지_Re_NEWable_Weekly_10월_3주차_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>에너지/유틸</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>교보증권</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>조혜빈</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Re-NEWable Weekly (10월 3주차 코멘트)</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr"/>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S223" s="3" t="inlineStr"/>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>2030년 국내 재생에너지 100GW 달성을 위해 2027년부터 연 10GW 이상, 2029~30년 연 15GW 확대를 목표로 설정함.</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>10년간 1,000조원을 투입하는 K-GX를 통해 태양광·풍력 핵심부품 국내생산세액공제 등 강력한 공급망 지원 정책을 추진함.</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>미국 태양광 제조 증설 계획의 70% 이상이 자금 미확보 또는 좌초 상태로, 실제 생산량과 발표 CAPA 간의 격차가 부각됨.</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>국내 재생에너지 확대 정책과 글로벌 공급망 규제 강화 속에서 핵심 부품 국산화 및 공급망 안정화가 산업 성장의 핵심 변수로 작용할 전망이다.</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2030년 재생에너지 목표 100GW | K-GX 투입 예산 1,000조원 | 미국 태양광 증설 계획 좌초 비중 70%</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>OCI홀딩스, SK이터닉스, HD현대에너지솔루션, 씨에스윈드</t>
+        </is>
+      </c>
+      <c r="AD223" s="6" t="n">
+        <v>4153.7</v>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218418</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218418_산업_에너지_Re_NEWable_Weekly_10월_3주차_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B224" t="n">
+        <v>218422</v>
+      </c>
+      <c r="C224" s="5" t="n">
+        <v>46307.56710648148</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>산업_음식료_키움_음식료_Weekly_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>음식료</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>박상준</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>키움 음식료 Weekly (10/12)</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr"/>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S224" s="3" t="inlineStr"/>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>1. 삼양식품은 신제품 짜장라면 '짜르르'를 내년 1분기 미국과 일본 시장에 출시해 프리미엄 라면 브랜드 확장을 추진할 계획입니다.</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2. KT&amp;G는 인도네시아 신공장 가동으로 연간 최대 350억 개비 생산 능력을 확보하며 해외 최대 생산 거점으로서의 입지를 강화했습니다.</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>3. CJ제일제당은 인도 벵갈루루에 '비비고 밥상' 1호점을 개장하며 K푸드 영토 확장을 가속화하고 현지 시장 공략을 본격화하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>국내 음식료 기업들이 해외 생산 거점 확대와 현지 맞춤형 신제품 출시를 통해 글로벌 시장 점유율을 적극적으로 높이고 있습니다.</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>인도네시아 연간 최대 생산 능력 350억 개비 | 해외 설비 투자 총액 2조 4000억원 | 대인도 농식품 수출액 YoY 증가율 18.9% | 롯데웰푸드 빼빼로 광고 조회수 1000만뷰</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>KT&amp;G, CJ제일제당, 롯데웰푸드, 농심</t>
+        </is>
+      </c>
+      <c r="AD224" s="6" t="n">
+        <v>465.3</v>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218422</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218422_산업_음식료_키움_음식료_Weekly_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B225" t="n">
+        <v>218426</v>
+      </c>
+      <c r="C225" s="5" t="n">
+        <v>46307.56719907407</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>산업_자동차_수요는_못_바꿔도_물량은_되찾는다_하나증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>자동차</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>하나증권</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>송선재</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>완성차 지역별 판매 동향 (2026년 9월): 수요는 못 바꿔도, 물량은 되찾는다</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr"/>
+      <c r="Q225" s="2" t="inlineStr"/>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S225" s="3" t="inlineStr"/>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>1. 현대차·기아 9월 합산 도매판매는 전년 대비 7% 감소하며 물량 기준 저성장이 지속됨.</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2. 산업수요 둔화와 경쟁 심화 외에도 생산 차질 및 모델 노후화가 실적에 복합적 영향을 미침.</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>3. 생산 차질 해소와 신차 출시 효과가 본격화되면서 향후 시장 점유율 반등이 기대됨.</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>생산 차질 해소와 신차 라인업 확대를 통해 완성차 업체의 시장 점유율 반등이 예상됩니다.</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>현대차 목표주가 510000 | 기아 목표주가 170000 | 현대차 9월 도매판매 308000대 | 기아 9월 도매판매 281000대</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="AD225" s="6" t="n">
+        <v>2770.1</v>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218426</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218426_산업_자동차_수요는_못_바꿔도_물량은_되찾는다_하나증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B226" t="n">
+        <v>218430</v>
+      </c>
+      <c r="C226" s="5" t="n">
+        <v>46307.56725694444</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>산업_제약_Kiwoom_Healthcare_종합정리_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>바이오/제약</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>키움증권</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>허혜민, 신민수, 김종현</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Kiwoom Healthcare 종합정리 (2026년 10월 12일)</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr"/>
+      <c r="Q226" s="2" t="inlineStr"/>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S226" s="3" t="inlineStr"/>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>1. 한미약품 비만신약 에페가 국내 최초로 식약처 허가를 획득하며 상용화 사례를 기록함.</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2. 펩트론은 릴리와의 약물전달 플랫폼 기술평가를 종료했으나 협력 가능성은 열어둠.</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>3. 10월 초순 의료기기 수출 지표에서 필러와 덴탈 임플란트 등 주요 품목이 전년 대비 높은 성장세를 보임.</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>국내 제약·바이오 기업들의 신약 개발 성과와 의료기기 수출 지표의 견조한 흐름이 지속되고 있음.</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>에페 체중 감소율 9.75% | 알테오젠 투자 유치 2000억 원 | 10월 초순 필러 수출액 1억 1만 달러 | 10월 초순 덴탈 임플란트 수출액 2172만 달러</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>펩트론, 알테오젠, 오름테라퓨틱, 파마리서치</t>
+        </is>
+      </c>
+      <c r="AD226" s="6" t="n">
+        <v>1295.5</v>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218430</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218430_산업_제약_Kiwoom_Healthcare_종합정리_1012_키움증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B227" t="n">
+        <v>218434</v>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>46307.56770833334</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>산업_조선_한수위_FSRU_개조신조_수요_확대_SK증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>한승한</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>FSRU 개조&amp;신조 수요 확대</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr"/>
+      <c r="Q227" s="2" t="inlineStr"/>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S227" s="3" t="inlineStr"/>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>1. 글로벌 FSRU 수요가 신규 수입국 확대와 아시아 데이터센터 가스 수요 증가로 사상 최대치를 기록 중임.</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2. LNGC 신조 슬롯 부족과 빠른 인도 일정, 저렴한 비용으로 인해 단기적으로 개조 수요가 폭발적으로 증가하고 있음.</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>3. 한국 조선소는 LNGC 교체 물량 수주와 고사양 신조 FSRU 수주, 개조 사업 수혜로 장기적 성장이 기대됨.</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>FSRU 시장은 공급 부족으로 개조 수요가 단기적으로 시장을 주도하며, 향후 고사양 신조 발주로 이어지는 구조적 성장이 전망됨.</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>신조선가지수 186.73pt | 중고선가지수 224.04pt | FSRU 신조 계약선가 319.7~328.4백만달러 | 글로벌 FSRU 수주잔고 20척 근접 전망</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>한화엔진, HD현대마린솔루션</t>
+        </is>
+      </c>
+      <c r="AD227" s="6" t="n">
+        <v>797.8</v>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218434</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218434_산업_조선_한수위_FSRU_개조신조_수요_확대_SK증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B228" t="n">
+        <v>218438</v>
+      </c>
+      <c r="C228" s="5" t="n">
+        <v>46307.56778935185</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>산업_철강금속_Steel_Weekly_10월_2주차_iM증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>철강/금속</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>풍산</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>iM증권</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>김윤상</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>iM Steel Weekly (10월 2주): 미국 제외 글로벌 철강 업황 둔화 및 매크로 불확실성 지속</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr"/>
+      <c r="Q228" s="2" t="inlineStr"/>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S228" s="3" t="inlineStr"/>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>달러</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>1. 미국을 제외한 글로벌 철강 업황은 수요 부진과 원료탄 가격 약세로 전반적인 약보합세가 지속됨.</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2. 중국은 국경절 연휴 이후에도 거래가 한산하고 유통 재고가 크게 증가하며 업황 개선이 불투명함.</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>3. 국내 철강 유통 가격은 저가 수입재 유입 우려와 수요 부진으로 당분간 약세 흐름이 불가피함.</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>글로벌 철강 업황의 둔화와 매크로 불확실성이 지속되는 가운데, 국내 철강 업계는 수입재 유입과 수요 부진으로 당분간 정체 국면이 이어질 전망입니다.</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>베트남 열연가격 535달러 | 미국 8월 철강 수입량 235만숏톤 | 중국 철강재 유통재고 1251만톤 | 미시간대 기대인플레이션 1년 4.7%</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>부정</t>
+        </is>
+      </c>
+      <c r="AA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>현대제철, Arcelormittal, Nucor</t>
+        </is>
+      </c>
+      <c r="AD228" s="6" t="n">
+        <v>1938.7</v>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218438</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218438_산업_철강금속_Steel_Weekly_10월_2주차_iM증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B229" t="n">
+        <v>218442</v>
+      </c>
+      <c r="C229" s="5" t="n">
+        <v>46307.5678587963</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>산업_항공운송_Aviation_Industry_9월_항공_데이터_기록적인_3분기_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>운송</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>양승윤</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>9월 항공 데이터: 기록적인 3분기</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr"/>
+      <c r="Q229" s="2" t="inlineStr"/>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S229" s="3" t="inlineStr"/>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>3분기 국제선 여객은 2,636만명으로 분기 사상 최고치를 경신하며 견조한 수요를 기록함.</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>인천공항 화물 물동량은 27만톤으로 전년 대비 10% 증가하며 견조한 수준을 지속함.</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>대한항공은 AI·반도체 화물 수요와 아시아나항공 합병 시너지로 수익성 개선이 기대됨.</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>항공업종은 견조한 여객 수요와 화물 운임 강세에 힘입어 실적 호조가 지속될 전망입니다.</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>9월 국제선 여객 834만명 | 인천공항 화물 물동량 27만톤 | 3분기 국제선 여객 2636만명 | 10월 국제선 유류할증료 23단계</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>아시아나항공</t>
+        </is>
+      </c>
+      <c r="AD229" s="6" t="n">
+        <v>805.2</v>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218442</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218442_산업_항공운송_Aviation_Industry_9월_항공_데이터_기록적인_3분기_유진투자증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B230" t="n">
+        <v>218446</v>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>46307.56792824074</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>산업_화장품_아마존_프라임데이_결과_코멘트_K_뷰티_good_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>산업</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>화장품/생활용품</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>메디큐브</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>교보증권</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>권우정</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>아마존 프라임 빅딜데이 코멘트: 이번에도 대박</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr"/>
+      <c r="Q230" s="2" t="inlineStr"/>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="S230" s="3" t="inlineStr"/>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>불명</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>10월 아마존 프라임 빅딜데이 미국 Top 100 내 K-뷰티 비중은 B&amp;P 32%, 스킨케어 46%로 지난 6월 대비 각각 확대됨.</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>메디큐브는 6개국 아마존 B&amp;P Top 100 진입 SKU 수가 3월 38개에서 9월 93개로 폭발적 성장을 기록하며 시장 지배력 강화.</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>유럽 주요국 내 K-뷰티 브랜드들의 순위가 전반적으로 상승하며 북미를 넘어 유럽 시장으로의 확장세가 가속화되고 있음.</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>아마존 행사에서 확인된 K-뷰티의 글로벌 점유율 확대는 화장품 업종의 견조한 성장성을 증명하며 조정 시 매수 전략이 유효함을 시사함.</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>미국 스킨케어 K-뷰티 비중 46% | 메디큐브 6개국 진입 SKU 93개 | 미국 B&amp;P K-뷰티 비중 32% | 스페인 B&amp;P K-뷰티 비중 38%</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>긍정</t>
+        </is>
+      </c>
+      <c r="AA230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>아누아, 라네즈, 달바, 조선미녀</t>
+        </is>
+      </c>
+      <c r="AD230" s="6" t="n">
+        <v>555.2</v>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>https://t.me/DOC_POOL/218446</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>C:\ivybots\out\docpool_daily\pdf\2026-10-14\218446_산업_화장품_아마존_프라임데이_결과_코멘트_K_뷰티_good_교보증권_261012.pdf</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG203"/>
+  <autoFilter ref="A1:AG230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53501,7 +60893,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -53597,7 +60989,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>29</t>
         </is>
       </c>
     </row>
